--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_huanyingdaoshi.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_huanyingdaoshi.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="20145" windowHeight="11565"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
     <t>1#99</t>
   </si>
   <si>
-    <t>物理攻击力+20，魔法攻击力+40，防御力+20，\n生命值+50，魔法值+25\n持续8小时，死亡消失&lt;color=#4C961D&gt;(白银特权：死亡不消失)&lt;/color&gt;</t>
+    <t>物理攻击力+30，魔法攻击力+80，防御力+30，\n生命值+100，魔法值+40\n持续8小时，死亡消失&lt;color=#4C961D&gt;(畅玩卡死亡不消失)&lt;/color&gt;</t>
   </si>
   <si>
     <t>100#999</t>
